--- a/WorkBot/main/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,190 +482,316 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>39192</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bag Paper - Handle (Small)</t>
+          <t>Container - Paper Clamshell (Bagel Box)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>41.87</v>
+        <v>69.94</v>
       </c>
       <c r="E6" t="n">
-        <v>41.87</v>
+        <v>139.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>39192</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Container - Paper Clamshell (Bagel Box)</t>
+          <t>Cup - Cold (16oz)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>69.94</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>139.88</v>
+        <v>84.43000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cup - Cold (16oz)</t>
+          <t>Toilet Paper</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>84.43000000000001</v>
+        <v>46.28</v>
       </c>
       <c r="E8" t="n">
-        <v>84.43000000000001</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Toilet Paper</t>
+          <t>Towel Disp Folded</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>46.28</v>
+        <v>55.23</v>
       </c>
       <c r="E9" t="n">
-        <v>46.28</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>34365</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Towel Disp Folded</t>
+          <t>Wrap - Cold Sandwich (18" x 18")</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>55.23</v>
+        <v>102.85</v>
       </c>
       <c r="E10" t="n">
-        <v>55.23</v>
+        <v>102.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40834</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trash Bag (38x58)</t>
+          <t>Cup - Cold (24oz)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>45.73</v>
+        <v>70.67</v>
       </c>
       <c r="E11" t="n">
-        <v>91.45999999999999</v>
+        <v>70.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wrap - Cold Sandwich (18" x 18")</t>
+          <t>Lid - Soup (6/16 oz)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>102.85</v>
+        <v>39.58</v>
       </c>
       <c r="E12" t="n">
-        <v>102.85</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cup - Cold (24oz)</t>
+          <t>Lid Anchor - 12oz (Dome)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>70.67</v>
+        <v>114.31</v>
       </c>
       <c r="E13" t="n">
-        <v>70.67</v>
+        <v>228.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>41788</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lid - Soup (6/16 oz)</t>
+          <t>Container - Anchor (16oz)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>39.58</v>
+        <v>49.13</v>
       </c>
       <c r="E14" t="n">
-        <v>39.58</v>
+        <v>147.39</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>41789</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Container - Anchor (24oz)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="E15" t="n">
+        <v>154.74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>41787</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Container - Anchor 16oz (microwavable)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="E16" t="n">
+        <v>209.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>22435</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Container - Deli (16oz)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="E17" t="n">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15509</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Container - Deli (32oz)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>64.73999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>41399</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cup - Cold (12oz)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>84.95999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>40007</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Bowl (Smoothie)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>39.9</v>
       </c>
     </row>
   </sheetData>
